--- a/ai-gate/copy.xlsx
+++ b/ai-gate/copy.xlsx
@@ -3,20 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF6FE0F-7A9C-6749-822F-A59FA0F3B651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404349CD-B0A3-9242-8DB7-9C06B6A7E81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
     <sheet name="LEVANT_AR" sheetId="2" r:id="rId2"/>
+    <sheet name="AFRICA_FR" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="242">
   <si>
     <t>Type</t>
   </si>
@@ -490,12 +491,398 @@
     <t>ssss</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Une femme passe et la lumière s'allume automatiquement. La phrase ''Sensation intelligente'' apparaît à l'écran.
+Un homme et une femme s'embrassent tandis que l'enceinte XBOOM s'active, accompagnée de la phrase ''Compréhension profonde''.
+Un homme est assis tristement au volant. Le logo LG AI apparaît avec la phrase ''Attention chaleureuse''.
+Un match de football est diffusé à la télévision. L'IA LG répond par une interaction vocale. La phrase ''Pour une vie agréable'' apparaît ci-dessous.
+XBOOM, la télévision et une famille assise sur le canapé avec leur chien apparaissent dans un seul cadre.
+Une mère et son fils utilisent la machine à laver ensemble. La phrase ''Pour une vie facile'' apparaît.
+Des scènes de la mère et du fils, un gros plan sur le bouton AI Wash et un homme utilisant l'ordinateur portable LG Gram sont superposées sur un seul plan, avec la phrase ''Pour une vie facile''.
+Un homme et une femme sont assis à l'avant d'une voiture. Le logo LG AI apparaît entre eux, accompagné de la phrase ''Pour votre puits''. Une vie bienveillante.
+Une personne entre dans un bureau avec son chien. Le purificateur d'air se met en marche.
+Plan final : un fond blanc avec le logo LG AI et la phrase ''Votre Allié Intelligent''.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI logo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chez LG, nous nous sommes demandés : à quoi sert l'IA ? &lt;br&gt;
+              Après mûre réflexion, nous avons trouvé la réponse. &lt;br&gt;&lt;br&gt;
+              Pour nous, l'IA va au-delà de l'Intelligence Artificielle, c'est une Intelligence Affectueuse. &lt;br&gt;&lt;br&gt;
+              A mesure qu'elle s'intègre à notre quotidien, &lt;br&gt;
+              elle doit contribuer à améliorer notre quotidien. &lt;br&gt;&lt;br&gt;
+              C'est pourquoi VOUS êtes au centre de notre réfléxion.
+              &lt;strong&gt;Découvrez Life's Good avec LG AI&lt;/strong&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une vie merveilleuse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pour votre vie merveilleuse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un homme et une femme sont assis sur le canapé et regardent un match de foot sur un téléviseur LG dans le salon. La scène change et l'homme et la femme s'enlacent. La caméra se concentre sur la LG XBOOM à côté d'eux.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI comprend votre vie et améliore vos expériences pour rendre votre vie remplie de moments agréables.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une vie sans effort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une vie bien soignée</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apprendre Encore Plus</t>
+  </si>
+  <si>
+    <t>Vue de face du produit LG OLED evo AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG OLED  AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/television/lg-oled83c56la</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/oled-tvs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/qned-tvs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/nanocell-tvs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG Nanocell  AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une mère et son fils utilisent ensemble une machine à laver LG AI, tournant le cadran pour activer AI Wash. Un homme utilisant l'ordinateur portable LG gram apparaît dans la même séquence.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pour votre vie sans effort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/washing-machines/lg-wt1310rh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG WashTower AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/washing-machines/lg-f0l9dgp2s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/refrigerators/lg-gc-x24ffcab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG InstaView AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI prend soin de vous, de votre espace et de la planète pour rendre votre vie bien entretenue, comme vous le désirez.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un homme entre dans le bureau, tenant un chien en laisse. L'homme au volant a l'air triste tandis que l'IA LG lui montre une photo de famille. L'écran de la voiture s'affiche en gros plan tandis que l'IA LG affiche une carte et revisite un souvenir.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/global/mobility/mobility-labworks-series/adas-solutions/in-cabin-vision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utilisateur interagissant avec l'interface à écran tactile alimentée par une solution IHM IA multimodale, sélectionnant le menu du café avec l'invite de l'assistant IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/global/mobility/mobility-labworks-series/digital-cockpit-solutions/digital-cockpit-gamma</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Climatisation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Appareils électroménagers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Le téléviseur LG AI apprend vos préférences de visionnage et comprend votre style de vie pour optimiser chaque aspect de votre expérience télévisuelle, créant ainsi un divertissement personnalisé idéal rien que pour vous.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">téléviseur LG AI </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez la nouvelle génération de&lt;br&gt;
+                          téléviseurs LG AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/television/ai-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sur l'écran d'un téléviseur LG OLED, la page d'accueil webOS 25 regorge d'applications et de contenus de divertissement. À côté du téléviseur se trouve la télécommande LG AI Magic ; le bouton IA est mis en surbrillance comme s'il était activé par la voix. Une bulle de dialogue apparaît à côté : ''Suggérer un film que j'aime".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Écran de téléviseur LG OLED montrant le fonctionnement de la recherche IA. Une petite fenêtre de discussion s'ouvre, montrant comment l'utilisateur a demandé quels jeux de sport étaient disponibles. La recherche IA a répondu par chat et en affichant des vignettes des différents contenus disponibles. Une invite permet également de demander à Microsoft Copilot.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La télécommande LG AI Magic en action. Une brève pression sur le bouton AI active l'assistant IA sur l'écran du téléviseur OLED, qui suggère ensuite des mots-clés.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un contenu de science-fiction est diffusé sur un téléviseur OLED LG. À gauche de l'écran se trouve l'interface du chatbot IA. L'utilisateur signale au chatbot que l'écran est trop sombre et celui-ci propose des solutions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Femme chantant dans un microphone avec un casque, mise en valeur par l'amélioration du son du processeur LG α11 AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deux scènes connectées avec la télécommande LG AI Magic Remote devant un téléviseur : la première montrant une scène de science-fiction, la seconde montrant un écran d'accueil avec du contenu personnalisé</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Les fonctionnalités d'IA de LG utilisent des algorithmes entraînés par l'apprentissage profond pour la mise à l'échelle de l'image et le mixage audio en temps réel.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**Tous les téléviseurs LG webOS 24 sont dotés de la personnalisation par IA, à l'exception de ceux sans capteur de lumière.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-audio-eyebrow-logo-desktop.svg" alt="Audio" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Cela semble particulièrement juste</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-tv-eyebrow-logo-desktop.svg" alt="TV" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Évolue pour satisfaire tous vos besoins de divertissement</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG xboom AI analyse et ajuste le son en fonction du genre et de l'espace. Grâce à l'éclairage IA qui sublime l'ambiance et s'harmonise avec votre musique, vous profitez d'un son et d'une ambiance uniques.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme et un homme s'embrassent dans le salon, avec l'enceinte XBOOM allumée à côté d'eux.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profitez d'une nouvelle expérience sonore &lt;br&gt;
+                          avec LG xboom AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enceinte LG XBOOM avec modes sonores IA, notamment Bass Boost, Voice Enhance et Standard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enceinte LG XBOOM avec éclairage IA qui s'adapte aux modes voix, ambiance et fête</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enceinte LG XBOOM placée sur une table dans une pièce aux tons rouges avec des murs à motifs quadrillés et des meubles modernes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-appliances-eyebrow-logo-desktop.svg" alt="Appareils électroménagers" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Allégez toutes vos charges</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG WashTower AI détecte ce que vous lavez pour fournir un lavage optimisé pour le soin des tissus sensibles, vous assurant ainsi de perfectionner sans effort chaque charge, à chaque fois.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez un nouveau mode de vie &lt;br&gt;
+                          avec LG AI Core Tech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laveuse et sécheuse superposées LG intégrées dans une buanderie moderne avec armoires en bois et banquette</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Réglage manuel du cycle de lavage AI sur la machine à laver LG à l'aide du cadran de commande intelligent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L'utilisateur sélectionne le cycle de séchage AI sur le sèche-linge LG à l'aide du cadran de commande numérique</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Ce produit sera commercialisé progressivement dans certains pays.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**La détection IA est activée lorsque la charge est inférieure à 6 kg.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***Le lavage IA doit être utilisé uniquement avec des tissus similaires [tous les tissus ne sont pas détectés] et une lessive adaptée.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****Le séchage IA est disponible uniquement pour les charges inférieures à 5 kg avec des tissus présentant le même niveau d'absorption d'humidité. »</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-air-conditioning-eyebrow-logo-desktop.svg" alt="Climatisation" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Confort avec un refroidissement parfaitement réglé</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG DUALCOOL AI assure une qualité d'air optimale pour votre confort tout en optimisant l'efficacité énergétique pour vous aider à réduire vos coûts. Avec LG AI Air, profitez d'une climatisation parfaitement adaptée à votre confort.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez un confort optimisé &lt;br&gt;
+                          avec LG AI Air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Le climatiseur LG DUAL Inverter refroidit un salon moderne, où une femme est assise sur le canapé, alimenté par la technologie ThinQ AI.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme se détend dans un salon intelligent tandis que le climatiseur LG AI ajuste automatiquement la température, le débit d'air et l'humidité</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interface smartphone affichant un graphique de consommation d'énergie devant le climatiseur LG, mettant en évidence AI kW Manager pour une surveillance efficace de la puissance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*L'AI Air peut être commandé via une télécommande et ThinQ.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**L'AI Air est disponible en modes refroidissement et chauffage.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***Lors de l'utilisation de l'AI Air, le volume d'air et la direction du vent s'ajustent automatiquement en fonction de la situation, et l'AI Air se désactive lorsque la direction du vent change.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****Lorsque l'AI Air est activé, le capteur radar détecte la position de l'occupant et active automatiquement le vent direct/indirect.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*****La distance de détection du capteur radar peut atteindre 5 m, et des différences peuvent survenir selon l'installation et l'environnement d'utilisation du produit.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*****Cette fonction est uniquement compatible avec les modèles équipés de capteurs radar.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThinQ® vous aide à réaliser votre vie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plateforme pour vos appareils et appareils intelligents LG, ThinQ met le contrôle et la commodité à portée de main, pour vous aider à simplifier la vie et à profiter du confort de la maison.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/africa_fr/lg-thinq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une personne tient un smartphone avec l'application LG ThinQ ouverte, gérant des appareils domestiques intelligents tout en buvant du café.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dans une cuisine intelligente moderne, une femme utilise une commande vocale pour démarrer la machine à laver avec LG ThinQ AI, tandis qu'un homme lit sur le canapé en arrière-plan.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contrôle simple avec l'assistant vocal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dites à votre appareil LG exactement ce dont vous avez besoin en le disant simplement, et le haut-parleur IA écoutera et vérifiera le cycle pour vous le faire savoir.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un smartphone affiche l'application LG ThinQ contrôlant le four coulissant LG InstaView, permettant un entretien efficace des produits dans la cuisine.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintenance efficace des produits</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grâce à l'application LG ThinQ, vérifiez votre appareil LG, téléchargez de nouveaux cycles, surveillez l'utilisation des cycles et bien plus encore.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>En savoir plus sur LG Affectionate Intelligence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un dirigeant de LG Electronics détient un certificat d'accréditation en cybersécurité, avec un graphique de sécurité numérique en arrière-plan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG renforce son leadership en matière de cybersécurité avec l'accréditation KOLAS IoT Cybersecurity Testing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lgnewsroom.com/2025/01/lg-strengthens-cybersecurity-leadership-with-kolas-iot-cybersecurity-testing-accreditation/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Les visiteurs admirent l'écran LED incurvé de LG arborant le slogan « Life's Good 24/7 » lors d'une exposition technologique</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG présente ses dernières innovations, propulsées par « Affectionate Intelligence », au CES 2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intervenant présentant des solutions B2B basées sur l'IA sur scène lors d'un événement LG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG dévoile une journée dans la vie avec "Affectionate Intelligence'' lors de la première mondiale de LG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +902,14 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -540,15 +935,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -913,7 +1314,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3553,4 +3954,1268 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CECDB3-77B8-B245-85F1-872FFBD72961}">
+  <dimension ref="A1:B165"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="234">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="126">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="54">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="36">
+      <c r="A66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>2</v>
+      </c>
+      <c r="B70" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>2</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>2</v>
+      </c>
+      <c r="B74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>2</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>2</v>
+      </c>
+      <c r="B80" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="54">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="36">
+      <c r="A87" t="s">
+        <v>2</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>2</v>
+      </c>
+      <c r="B91" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>2</v>
+      </c>
+      <c r="B95" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="54">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>2</v>
+      </c>
+      <c r="B99" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>4</v>
+      </c>
+      <c r="B100" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="36">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>4</v>
+      </c>
+      <c r="B104" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>2</v>
+      </c>
+      <c r="B105" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>4</v>
+      </c>
+      <c r="B106" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>2</v>
+      </c>
+      <c r="B107" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="54">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>4</v>
+      </c>
+      <c r="B113" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>2</v>
+      </c>
+      <c r="B114" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="36">
+      <c r="A116" t="s">
+        <v>2</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>2</v>
+      </c>
+      <c r="B120" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>4</v>
+      </c>
+      <c r="B121" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>2</v>
+      </c>
+      <c r="B122" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>2</v>
+      </c>
+      <c r="B125" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+      <c r="B142" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>2</v>
+      </c>
+      <c r="B148" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>4</v>
+      </c>
+      <c r="B150" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>2</v>
+      </c>
+      <c r="B151" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>4</v>
+      </c>
+      <c r="B154" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>2</v>
+      </c>
+      <c r="B155" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>14</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>4</v>
+      </c>
+      <c r="B158" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>2</v>
+      </c>
+      <c r="B159" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>4</v>
+      </c>
+      <c r="B162" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>2</v>
+      </c>
+      <c r="B163" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{F43A1E02-44B8-3642-A3AF-A032972319BB}"/>
+    <hyperlink ref="B15" r:id="rId2" xr:uid="{BDAD240A-8C87-0042-8EAD-BE09CE537A45}"/>
+    <hyperlink ref="B18" r:id="rId3" xr:uid="{992A67C6-2A4A-AC41-A937-1C273FF25DE9}"/>
+    <hyperlink ref="B21" r:id="rId4" xr:uid="{E5660A9B-B304-4B45-B02F-0075BBF31DFF}"/>
+    <hyperlink ref="B30" r:id="rId5" xr:uid="{A908065C-B2FA-E743-B3C8-8AE701A9666B}"/>
+    <hyperlink ref="B33" r:id="rId6" xr:uid="{87730795-4A89-3040-97E0-8E1D8B65BAD5}"/>
+    <hyperlink ref="B39" r:id="rId7" xr:uid="{AC67B0C6-A78B-5F46-B03D-C18D4E1D894B}"/>
+    <hyperlink ref="B48" r:id="rId8" xr:uid="{55E33A50-7572-924C-A799-E340AD254DDE}"/>
+    <hyperlink ref="B54" r:id="rId9" xr:uid="{F2E7B405-77FD-5946-9AAB-40A95243C884}"/>
+    <hyperlink ref="B51" r:id="rId10" xr:uid="{0C9C4D40-8F39-2F45-B499-549596017A90}"/>
+    <hyperlink ref="B68" r:id="rId11" xr:uid="{DC33F75E-1728-4041-9C09-C8631C4069F6}"/>
+    <hyperlink ref="B145" r:id="rId12" xr:uid="{6B263608-70DE-BA46-9EE6-09951BD7527B}"/>
+    <hyperlink ref="B157" r:id="rId13" xr:uid="{5645AD79-F4FC-0C48-BD64-925171F4A3B8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>
--- a/ai-gate/copy.xlsx
+++ b/ai-gate/copy.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A360F4D1-A697-D345-9B47-7859D26FDA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C772067C-99E9-484A-8429-ABC552EEC542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34580" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
     <sheet name="LEVANT_AR" sheetId="2" r:id="rId2"/>
     <sheet name="AFRICA_FR" sheetId="4" r:id="rId3"/>
+    <sheet name="BE_FR" sheetId="5" r:id="rId4"/>
+    <sheet name="TN_FR" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="476">
   <si>
     <t>Type</t>
   </si>
@@ -182,10 +184,6 @@
     <t>Computing</t>
   </si>
   <si>
-    <t>&lt;img src="./assets/image/ai-product-category-tv-eyebrow-logo-desktop.svg" alt="LG AI TV" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
-                      Evolves to satisfy your every entertainment need</t>
-  </si>
-  <si>
     <t>LG AI TV</t>
   </si>
   <si>
@@ -244,10 +242,6 @@
     <t>**All LG webOS 24 TVs feature AI Customization, excluding those without light sensors.</t>
   </si>
   <si>
-    <t>&lt;img src="./assets/image/ai-product-category-audio-eyebrow-logo-desktop.svg" alt="LG AI Audio" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
-                      Sounds uniquely right</t>
-  </si>
-  <si>
     <t>LG AI Audio</t>
   </si>
   <si>
@@ -285,10 +279,6 @@
     <t>*This product is not available yet.</t>
   </si>
   <si>
-    <t>&lt;img src="./assets/image/ai-product-category-appliances-eyebrow-logo-desktop.svg" alt="LG AI Appliances" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
-                      Lighten your every load</t>
-  </si>
-  <si>
     <t>LG AI Appliances</t>
   </si>
   <si>
@@ -377,10 +367,6 @@
   </si>
   <si>
     <t>******This function works only with models that have radar sensors.</t>
-  </si>
-  <si>
-    <t>&lt;img src="./assets/image/ai-product-category-computing-eyebrow-logo-desktop.svg" alt="LG AI Computing" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;  
-                      Powers everything you do</t>
   </si>
   <si>
     <t>LG AI Computing</t>
@@ -23294,6 +23280,711 @@
       </rPr>
       <t>جي</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>copy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;span class="gradient-text" data-tp="copy"&gt;Affectionate Intelligence&lt;/span&gt; for YOU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Une femme passe à côté de l'appareil tandis que la lumière s'allume automatiquement. La phrase « Percevoir avec sagesse » apparaît à l'écran.
+Un homme et une femme s'embrassent tandis que le haut-parleur de la XBOOM s'active, accompagné de la phrase « Comprendre profondément ».
+Un homme s'assied tristement sur le siège du conducteur. Le logo LG AI apparaît, accompagné de la phrase « Warm care ».
+Un match de football est diffusé à la télévision. LG AI répond par une interaction vocale. La phrase « For your enjoyable life » (Pour une vie agréable) apparaît en bas.
+La XBOOM, la télévision et une famille assise sur le canapé avec son chien apparaissent dans une même image.
+Une mère et son fils utilisent ensemble le lave-linge. La phrase « Pour une vie sans effort » apparaît.
+Les images de la mère et du fils, un gros plan du bouton AI Wash et un homme utilisant l'ordinateur portable LG gram sont fusionnées en une seule image, avec la phrase « For your effortless life » (Pour une vie sans effort).
+Un homme et une femme sont assis sur les sièges avant d'une voiture. Le logo LG AI apparaît entre eux, accompagné de la phrase « For your well-groomed life » (Pour une vie soignée).
+Une personne entre dans un bureau avec son chien. Le purificateur d'air se met en marche automatiquement.
+Plan final : fond blanc avec le logo LG AI et la phrase « Affectionate Intelligence for YOU ».</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI-logo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;span class="gradient-text" data-tp="copy"&gt;Affectionate Intelligence&lt;/span&gt; for JOU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chez LG, nous nous sommes demandé à quoi devrait servir l'IA. &lt;br&gt;
+              Après mûre réflexion, nous avons trouvé notre réponse. &lt;br&gt;&lt;br&gt;
+              Pour nous, l’IA dépasse la simple intelligence artificielle : c’est une intelligence bienveillante. &lt;br&gt;&lt;br&gt;
+              Au fur et à mesure que l'IA fait partie de notre vie quotidienne, &lt;br&gt;
+              elle devrait nous aider à réaliser la vie meilleure que nous méritons tous. &lt;br&gt;&lt;br&gt;
+              C'est pourquoi LG AI commence par VOUS, en détectant et en comprenant, &lt;br&gt;
+              afin de s'assurer qu'elle prend soin de votre vie.
+              &lt;strong&gt;Découvrez les avantages de la vie avec LG AI&lt;/strong&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icône pour faire défiler vers le bas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Belle vie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une vie soignée</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI comprend votre vie et améliore vos expériences pour remplir votre vie de beaux moments.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un homme et une femme sont assis sur le canapé et regardent une émission de football sur un téléviseur LG dans le salon. La scène change et l'homme et la femme se prennent dans les bras.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Votre belle vie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/tv-oled-evo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>En savoir plus</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/tv-oled</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/tvs-qned</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG QNED  AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/nanocell-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>En savoir plus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG UHD AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI reconnaît vos souhaits et vous propose des solutions pour que votre vie se déroule sans problème, à votre façon.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une mère et son fils utilisent ensemble un lave-linge LG AI et tournent le bouton pour activer AI Wash. Un homme utilisant l’ordinateur portable LG gram apparaît dans la même scène.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pour une vie sans effort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/menage/lg-f4wx809y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Vue de face du lave-linge LG AI </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/cuisine/lg-gsxe90evad</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI prend soin de vous, de votre espace et de la planète, pour rendre votre vie meilleure, exactement comme vous le souhaitez.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un homme entre dans un bureau en tenant une laisse de chien. Un homme assis sur le siège du conducteur regarde tristement tandis que LG AI lui montre une photo de famille. L’écran de la voiture est montré en gros plan pendant que LG AI affiche une carte et fait apparaître à nouveau un rappel.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pour votre vie soignée</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG DUALCOOL AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue latérale du produit système de vision ADAS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un utilisateur interagit avec une interface tactile pilotée par une solution HMI IA multimodale, et sélectionne un menu de café grâce à une invite d’assistant IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Appareils</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ordinateur</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-tv-eyebrow-logo-desktop.svg" alt="LG AI TV" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Se développe pour répondre à tous vos besoins en divertissement</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI TV analyse vos préférences de visionnage et comprend votre style de vie afin d’optimiser chaque aspect de votre expérience télévisuelle, pour vous offrir un divertissement idéalement personnalisé.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Au-dessus de la LG Magic Remote, sont affichées des fonctions telles que AI Voice ID, AI Search, AI Chatbot, AI Concierge, AI Picture Wizard et AI Sound Wizard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez la prochaine génération de &lt;br&gt;
+                          LG AI TV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/be_fr/televiseurs/ai-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sur l’écran d’une TV LG OLED, la page d’accueil webOS 25 est affichée, remplie d’applications et de contenus de divertissement. À côté de la TV se trouve la télécommande LG AI Magic Remote, avec le bouton AI mis en évidence comme s’il avait été activé par la voix de l’utilisateur. Une bulle de dialogue affiche : « suggest a movie I'll like » (« suggère un film que j’aimerai »). »</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sur l’écran de la TV LG OLED, on montre comment fonctionne AI Search. Une petite fenêtre de chat affiche la question de l’utilisateur concernant les matchs de sport disponibles. AI Search répond via le chat ainsi qu’avec des miniatures de différents contenus disponibles. Une invite permet également de poser une question à Microsoft Copilot.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utilisation de la LG AI Magic Remote. En appuyant brièvement sur le bouton AI, l’assistant IA s’active à l’écran de la TV OLED, puis il propose des mots-clés.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un contenu de science-fiction est diffusé sur un écran LG OLED TV. Sur le côté gauche de l’écran se trouve l’interface du chatbot IA. L’utilisateur envoie un message au chatbot indiquant que l’écran est trop sombre, et le chatbot propose des solutions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Une femme chante dans un micro avec un casque audio, mise en valeur par l’amélioration sonore grâce au processeur LG α11 AI. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deux scènes connectées avec la LG AI Magic Remote pour une TV — d’abord une scène de science-fiction, puis un écran d’accueil avec du contenu personnalisé.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Les fonctions IA de LG utilisent des algorithmes entraînés basés sur le deep learning pour la mise à l’échelle d’image en temps réel et le mixage audio.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**Toutes les TV LG webOS 24 sont équipées de la personnalisation IA, sauf les modèles sans capteurs de lumière.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-audio-eyebrow-logo-desktop.svg" alt="LG AI Audio" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Un son unique</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La LG XBOOM AI analyse et adapte le son au genre musical et à l’espace. Avec un éclairage IA qui améliore l’ambiance et s’accorde à votre musique, vous pouvez profiter d’un son et d’une atmosphère uniques.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Une femme et un homme s’embrassent dans le salon, tandis que l’enceinte XBOOM à côté d’eux est allumée. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profitez d’une nouvelle expérience sonore &lt;br&gt;
+                          avec LG XBOOM AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enceinte LG XBOOM avec modes sonores IA, notamment Bass Boost, Voice Enhance et Standard.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enceinte LG XBOOM avec éclairage IA qui s’adapte aux modes voix, environnement et fête.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enceinte LG XBOOM posée sur une table dans une pièce aux tons rouges, avec des murs à motif en grille et un mobilier moderne</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Dit product is niet beschikbaar in de Benelux.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI Appareils</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-appliances-eyebrow-logo-desktop.svg" alt="LG AI Appareils" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Rend chaque lessive plus légère</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG WashTower AI détecte ce que vous lavez et optimise le cycle pour un meilleur soin des tissus, afin que vous puissiez faire chaque lessive sans effort, à chaque fois.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lave-linge et sèche-linge empilés LG intégrés dans une buanderie moderne avec des placards en bois et des sièges de banc.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez une nouvelle façon de vivre &lt;br&gt;
+                          avec la technologie LG AI Core</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main réglant le programme AI Wash sur la machine à laver LG à l’aide d’un bouton rotatif intelligent.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’utilisateur sélectionne le programme AI Dry sur le sèche-linge LG à l’aide d’un bouton rotatif numérique.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Dry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Ce produit sera progressivement lancé dans certains pays.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**La détection IA s’active si la charge pèse moins de 6 kg.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***AI Wash doit être utilisé uniquement avec des textiles similaires [tous les tissus ne sont pas détectés] et avec un détergent adapté.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***AI Dry est disponible uniquement pour des charges de moins de 5 kg composées de tissus ayant le même niveau d’absorption d’humidité.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-air-conditioning-eyebrow-logo-desktop.svg" alt="LG AI Climatisation" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Confort avec une climatisation parfaitement réglée</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI Climatisation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG DUALCOOL AI garantit toujours une qualité d’air optimale, vous maintient confortable tout en optimisant l’efficacité énergétique et en réduisant les coûts. Avec LG AI Air, vous profitez d’une climatisation parfaitement ajustée à votre confort.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Le climatiseur LG DUAL Inverter refroidit un salon moderne avec vue sur la mer, propulsé par la technologie ThinQ AI.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez un confort optimal &lt;br&gt;
+                          avec LG AI Air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme se détend dans un salon intelligent pendant que le climatiseur LG AI ajuste automatiquement la température, le flux d’air et l’humidité.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">L’interface smartphone affiche un graphique de la consommation d’énergie du climatiseur LG, mettant en avant l’AI kW Manager pour une gestion efficace de l’énergie. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*L’AI Air peut être contrôlé avec la télécommande et ThinQ.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**L’AI Air est disponible en mode refroidissement comme en mode chauffage.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***Lors de l’utilisation de l’AI Air, le volume d’air et la direction du vent sont automatiquement ajustés en fonction de la situation, et l’AI Air s’éteint lorsque la direction du vent est modifiée.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****Lorsque l’AI Air est activé, le capteur radar détecte la position de l’occupant et active automatiquement le vent direct ou indirect.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*****La portée de détection du capteur radar est de 5 mètres maximum, et cette portée peut varier selon l’installation et l’environnement d’utilisation du produit.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>******Cette fonction est disponible uniquement sur les modèles équipés de capteurs radar.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-computing-eyebrow-logo-desktop.svg" alt="LG AI Ordinateur" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;  
+                      Donne de la puissance à tout ce que vous faites</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI Ordinateur</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG gram AI renforce votre travail, en ligne comme hors ligne. Trouvez et résumez vos fichiers hors ligne en toute sécurité avec Gram Chat embarqué, et augmentez votre productivité en ligne grâce à Gram Chat cloud alimenté par GPT-4o.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme utilise un ordinateur portable LG gram avec une configuration à double écran pour des visioconférences et du multitâche dans son bureau à domicile.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Libérez vos nouvelles possibilités &lt;br&gt;
+                          sans limites avec LG gram AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ordinateur portable LG gram avec IA embarquée et interface d’assistant intelligent à l’écran.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ordinateur portable LG gram avec IA Cloud affichant une interface d’assistant intelligent pour le support en ligne et la productivité.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Au début de l’utilisation du produit, certaines fonctions peuvent ne pas fonctionner parfaitement. Cela est dû à la nature de l’IA embarquée, qui nécessite un temps d’adaptation à l’utilisateur.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Gram Chat On-Device nécessite des tâches d’indexation pour trouver le contenu sur votre PC en combinant des mots avec des données, ce qui peut prendre un certain temps avant d’obtenir les résultats souhaités.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThinQ est une plateforme pour vos appareils et équipements intelligents LG, mettant le contrôle et la simplicité à portée de main, pour simplifier votre vie et profiter du confort de la maison.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThinQ® aide la vie à se réaliser</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une personne tient un smartphone avec l’application LG ThinQ ouverte, gérant les appareils intelligents de la maison tout en buvant un café.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dans une cuisine intelligente moderne, une femme utilise une commande vocale pour lancer la machine à laver avec LG ThinQ AI, tandis qu’un homme lit sur le canapé en arrière-plan.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contrôle simple avec l’assistant vocal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un smartphone affiche l’application LG ThinQ qui permet de contrôler le four LG InstaView Slide-In Range, facilitant ainsi un entretien efficace de l’appareil dans la cuisine.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dites simplement à votre appareil ce dont vous avez besoin, et l’enceinte IA écoute puis contrôle le cycle.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entretien efficace de vos appareils</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Via l’application LG ThinQ, vous pouvez contrôler votre appareil, télécharger de nouveaux cycles, vérifier l’utilisation des cycles, et bien plus encore.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un cadre de LG Electronics tient un certificat d’accréditation en cybersécurité, avec un graphique de sécurité numérique en arrière-plan.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG renforce son leadership en cybersécurité avec l’accréditation KOLAS pour les tests de cybersécurité IoT.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Des visiteurs regardent l’écran LED incurvé de LG avec le slogan ‘Life’s Good 24/7’ lors d’un salon technologique.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG présente ses dernières innovations propulsées par “Affectionate Intelligence” au CES 2025.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un intervenant présente des solutions B2B propulsées par l’IA sur scène lors d’un événement LG.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG dévoile une journée dans la vie avec “Affectionate Intelligence” lors de la première mondiale de LG.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme passe et la lumière s'allume automatiquement. La phrase « Sensing wisely » apparaît à l'écran. Un homme et une femme s'embrassent tandis que l'enceinte XBOOM s'active, accompagnée de la phrase « Understanding deeply ». Un homme est assis tristement au volant. Le logo LG AI apparaît avec la phrase « Caring warmly ». Un match de football est diffusé à la télévision. LG AI répond par une interaction vocale. La phrase « For your wonderful life » apparaît ci-dessous. XBOOM, la télévision et une famille assise sur le canapé avec leur chien apparaissent dans un seul cadre. Une mère et son fils utilisent la machine à laver ensemble. La phrase « For your effortless life » apparaît. Des scènes de la mère et du fils, un gros plan sur le bouton AI Wash et un homme utilisant l'ordinateur portable LG Gram sont superposées sur un seul plan, avec la phrase « For your effortless life ». Un homme et une femme sont assis à l'avant d'une voiture. Le logo LG AI apparaît entre eux, accompagné de la phrase « For your well cared life ». Une personne entre dans un bureau avec son chien. Le purificateur d'air s'allume en réponse. Dernier plan : un fond blanc avec le logo LG AI et la phrase « Affectionate Intelligence for YOU ».</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Logo LG AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;span class="gradient-text" data-tp="copy"&gt;Une intelligence affectueuse&lt;/span&gt; pour VOUS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icône de défilement vers le bas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une vie délicieuse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un homme et une femme sont assis sur le canapé et regardent un match de foot sur un téléviseur LG dans le salon. La scène change et l'homme et la femme s'enlacent. La caméra se focalise sur la LG XBOOM à côté d'eux.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pour une vie pleine de douceur</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/televiseurs/oled-innovation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plus d'informations</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/tvs-oled</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG OLED AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/tvs-qned</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LGVue de face du produit QNED AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/tvs-super-uhd-4k</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG NanoCell AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L'IA de LG détecte vos besoins et présente des solutions pour que votre vie s'écoule sans effort à votre rythme.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/lave-linge/lg-f4v5rgp2t</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG Vivace AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du produit LG Washing Machine AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue de face du sèche-linge LG AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/refrigerateurs/lg-gc-q22ftqel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pour votre vie bien soignée</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/climatiseurs-dual-cool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vue latérale du produit du système de vision ADAS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>téléviseur LG AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-tv-eyebrow-logo-desktop.svg" alt="téléviseur LG AI" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Évolue pour satisfaire tous vos besoins de divertissement</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Découvrez la nouvelle génération de &lt;br&gt;
+                          téléviseurs LG AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/televiseurs/ai-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sur l'écran d'un téléviseur LG OLED, la page d'accueil webOS 25 regorge d'applications et de contenus de divertissement. À côté du téléviseur se trouve la télécommande LG IA Magic ; le bouton IA est mis en surbrillance comme s'il était activé par la voix. Une bulle de dialogue apparaît à côté : « Suggérer un film que j'aime ».</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identification vocale IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recherche IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Concierge IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chatbot IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assistant image/son IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Télécommande magique IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Les fonctionnalités d'IA de LG utilisent des algorithmes entraînés par l'apprentissage profond pour la mise à l'échelle de l'image et le mixage sonore en temps réel.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**Tous les téléviseurs LG webOS 24 sont dotés de la personnalisation par IA, à l'exception de ceux sans capteurs de lumière.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI Appareils électroménagers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img src="./assets/image/ai-product-category-appliances-eyebrow-logo-desktop.svg" alt="LG AI Appareils électroménagers" class="eyebrow-logo" loading="lazy" data-tp="alt"&gt;
+                      Allégez toutes vos charges</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG Vivace AI détecte ce que vous lavez pour fournir un lavage optimisé pour le soin des tissus sensibles, vous assurant ainsi de perfectionner sans effort chaque charge, à chaque fois.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/electromenager</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lavage IA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IA sèche</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**La détection AI est activée lorsque la charge est inférieure à 6 kg.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***AI Wash ne doit être utilisé qu'avec des types de tissus similaires [tous les tissus ne sont pas détectés] et un détergent adapté.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****AI Dry est disponible uniquement pour les charges inférieures à 5 kg avec des tissus ayant le même niveau d'absorption d'humidité.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/climatisation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gestionnaire de kW AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***Lors de l'utilisation d'AI Air, le volume d'air et la direction du vent sont automatiquement ajustés en fonction de la situation, et AI Air s'éteint lorsque la direction du vent change.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****Lorsque AI Air est activé, le capteur radar détecte l'emplacement de l'occupant et active automatiquement le vent direct/indirect.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*****La distance de détection du capteur radar peut atteindre 5 m, et des différences peuvent exister selon l'installation et l'environnement d'utilisation du produit.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>******Cette fonction fonctionne uniquement avec les modèles équipés de capteurs radar.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/tn/lg-thinq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG dévoile une journée dans la vie avec « Affectionate Intelligence » lors de la première mondiale de LG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" alt="LG AI TV" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Evolves to satisfy your every entertainment need</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" alt="LG AI Audio" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Sounds uniquely right</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" alt="LG AI Appliances" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Lighten your every load</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-mobile.svg" alt="LG AI Air Conditioning" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Comforts with perfectly tuned cooling</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-computing-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-computing-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-computing-eyebrow-logo-mobile.svg" alt="LG AI Computing" class="eyebrow-logo" loading="lazy"&gt;  
+                      &lt;/picture&gt;
+                      Powers everything you do</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23725,7 +24416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -23753,31 +24444,31 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -23785,7 +24476,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -23793,7 +24484,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -23801,7 +24492,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -23809,7 +24500,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -23817,127 +24508,127 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -23945,7 +24636,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -23953,7 +24644,7 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -23961,127 +24652,127 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -24089,7 +24780,7 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -24097,7 +24788,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -24105,79 +24796,79 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -24185,7 +24876,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -24193,7 +24884,7 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -24201,7 +24892,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -24209,7 +24900,7 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -24217,7 +24908,7 @@
         <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -24225,39 +24916,39 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="162">
       <c r="A63" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" t="s">
-        <v>53</v>
+        <v>2</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -24265,111 +24956,111 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -24377,7 +25068,7 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -24385,7 +25076,7 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -24393,39 +25084,39 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="162">
       <c r="A84" t="s">
-        <v>4</v>
-      </c>
-      <c r="B84" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -24433,63 +25124,63 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -24497,7 +25188,7 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -24505,39 +25196,39 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="162">
       <c r="A98" t="s">
-        <v>4</v>
-      </c>
-      <c r="B98" t="s">
-        <v>86</v>
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B100" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -24545,47 +25236,47 @@
         <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B107" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -24593,7 +25284,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -24601,7 +25292,7 @@
         <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -24609,7 +25300,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -24617,7 +25308,7 @@
         <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -24625,39 +25316,39 @@
         <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="162">
       <c r="A113" t="s">
-        <v>4</v>
-      </c>
-      <c r="B113" t="s">
-        <v>100</v>
+        <v>2</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B114" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B116" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -24665,47 +25356,47 @@
         <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B121" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -24713,7 +25404,7 @@
         <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -24721,7 +25412,7 @@
         <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -24729,7 +25420,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -24737,7 +25428,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -24745,7 +25436,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -24753,7 +25444,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -24761,39 +25452,39 @@
         <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="180">
       <c r="A130" t="s">
-        <v>4</v>
-      </c>
-      <c r="B130" t="s">
-        <v>116</v>
+        <v>2</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B131" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B133" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -24801,47 +25492,47 @@
         <v>2</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B138" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B139" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -24849,7 +25540,7 @@
         <v>2</v>
       </c>
       <c r="B140" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -24857,7 +25548,7 @@
         <v>2</v>
       </c>
       <c r="B141" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -24865,7 +25556,7 @@
         <v>2</v>
       </c>
       <c r="B142" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -24873,7 +25564,7 @@
         <v>2</v>
       </c>
       <c r="B143" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -24881,23 +25572,23 @@
         <v>2</v>
       </c>
       <c r="B144" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B145" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B146" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -24905,15 +25596,15 @@
         <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B148" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -24921,23 +25612,23 @@
         <v>2</v>
       </c>
       <c r="B149" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B150" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B151" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -24945,7 +25636,7 @@
         <v>2</v>
       </c>
       <c r="B152" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -24953,23 +25644,23 @@
         <v>2</v>
       </c>
       <c r="B153" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B154" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -24977,31 +25668,31 @@
         <v>2</v>
       </c>
       <c r="B156" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B158" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -25009,31 +25700,31 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>143</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B162" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B163" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -25041,15 +25732,23 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
         <v>13</v>
       </c>
-      <c r="B165" t="s">
-        <v>146</v>
+      <c r="B166" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -25081,7 +25780,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -25089,7 +25788,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90">
@@ -25097,7 +25796,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -25113,7 +25812,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -25121,7 +25820,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -25129,7 +25828,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -25137,7 +25836,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -25145,7 +25844,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -25168,7 +25867,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -25176,7 +25875,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -25184,7 +25883,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -25192,7 +25891,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -25200,7 +25899,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -25208,7 +25907,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -25216,7 +25915,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -25224,7 +25923,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -25232,7 +25931,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -25240,7 +25939,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -25263,7 +25962,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -25271,7 +25970,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -25279,7 +25978,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -25332,7 +26031,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -25340,7 +26039,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -25348,7 +26047,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -25371,7 +26070,7 @@
         <v>2</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -25379,7 +26078,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -25387,7 +26086,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -25415,7 +26114,7 @@
         <v>4</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -25423,7 +26122,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -25436,7 +26135,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -25444,7 +26143,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -25452,7 +26151,7 @@
         <v>2</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -25460,7 +26159,7 @@
         <v>2</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -25468,7 +26167,7 @@
         <v>2</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -25486,7 +26185,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -25494,7 +26193,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -25502,7 +26201,7 @@
         <v>2</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -25510,7 +26209,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="36">
@@ -25518,7 +26217,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -25536,7 +26235,7 @@
         <v>4</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -25544,7 +26243,7 @@
         <v>2</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -25552,7 +26251,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -25560,7 +26259,7 @@
         <v>2</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -25568,7 +26267,7 @@
         <v>4</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -25576,7 +26275,7 @@
         <v>2</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -25584,7 +26283,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -25592,7 +26291,7 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -25600,7 +26299,7 @@
         <v>4</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -25608,7 +26307,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -25616,7 +26315,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -25624,7 +26323,7 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -25632,7 +26331,7 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -25640,7 +26339,7 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="54">
@@ -25648,7 +26347,7 @@
         <v>2</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -25656,7 +26355,7 @@
         <v>4</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -25664,7 +26363,7 @@
         <v>2</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -25672,7 +26371,7 @@
         <v>4</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="36">
@@ -25680,7 +26379,7 @@
         <v>2</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -25698,7 +26397,7 @@
         <v>4</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -25706,7 +26405,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -25714,7 +26413,7 @@
         <v>4</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -25722,7 +26421,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -25730,7 +26429,7 @@
         <v>4</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -25738,7 +26437,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -25746,7 +26445,7 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="54">
@@ -25754,7 +26453,7 @@
         <v>2</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -25762,7 +26461,7 @@
         <v>4</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -25770,7 +26469,7 @@
         <v>2</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -25778,7 +26477,7 @@
         <v>4</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="36">
@@ -25786,7 +26485,7 @@
         <v>2</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -25804,7 +26503,7 @@
         <v>4</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -25812,7 +26511,7 @@
         <v>2</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -25820,7 +26519,7 @@
         <v>4</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -25828,7 +26527,7 @@
         <v>2</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -25836,7 +26535,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -25844,7 +26543,7 @@
         <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -25852,7 +26551,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -25860,7 +26559,7 @@
         <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -25868,7 +26567,7 @@
         <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -26021,7 +26720,7 @@
         <v>2</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -26029,7 +26728,7 @@
         <v>2</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -26047,7 +26746,7 @@
         <v>4</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -26055,7 +26754,7 @@
         <v>4</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -26063,7 +26762,7 @@
         <v>2</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -26071,7 +26770,7 @@
         <v>2</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -26079,7 +26778,7 @@
         <v>4</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -26087,7 +26786,7 @@
         <v>2</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -26095,7 +26794,7 @@
         <v>2</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -26103,7 +26802,7 @@
         <v>2</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -26111,7 +26810,7 @@
         <v>4</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -26119,7 +26818,7 @@
         <v>2</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -26127,7 +26826,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -26135,7 +26834,7 @@
         <v>13</v>
       </c>
       <c r="B157" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -26143,7 +26842,7 @@
         <v>4</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -26151,7 +26850,7 @@
         <v>2</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -26159,7 +26858,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -26167,7 +26866,7 @@
         <v>13</v>
       </c>
       <c r="B161" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -26175,7 +26874,7 @@
         <v>4</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -26183,7 +26882,7 @@
         <v>2</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -26191,7 +26890,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -26199,7 +26898,7 @@
         <v>13</v>
       </c>
       <c r="B165" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -26237,7 +26936,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -26245,7 +26944,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="126">
@@ -26253,7 +26952,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -26269,7 +26968,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -26277,7 +26976,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -26285,7 +26984,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -26293,7 +26992,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -26301,7 +27000,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -26309,7 +27008,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -26317,7 +27016,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -26325,7 +27024,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -26333,7 +27032,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -26341,7 +27040,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -26349,7 +27048,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -26357,7 +27056,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -26365,7 +27064,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -26381,7 +27080,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -26389,7 +27088,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -26397,7 +27096,7 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -26405,7 +27104,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -26428,7 +27127,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -26436,7 +27135,7 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -26444,7 +27143,7 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -26452,7 +27151,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -26460,7 +27159,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -26468,7 +27167,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -26476,7 +27175,7 @@
         <v>13</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -26484,7 +27183,7 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -26492,7 +27191,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -26515,7 +27214,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -26523,7 +27222,7 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -26531,7 +27230,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -26554,7 +27253,7 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -26562,7 +27261,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -26578,7 +27277,7 @@
         <v>13</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -26594,7 +27293,7 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -26602,7 +27301,7 @@
         <v>13</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -26618,7 +27317,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -26626,7 +27325,7 @@
         <v>13</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -26634,7 +27333,7 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -26642,7 +27341,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -26666,7 +27365,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -26674,7 +27373,7 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -26687,7 +27386,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -26695,7 +27394,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -26703,7 +27402,7 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -26711,7 +27410,7 @@
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="36">
@@ -26719,7 +27418,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -26727,7 +27426,7 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -26735,7 +27434,7 @@
         <v>13</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -26743,7 +27442,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -26751,7 +27450,7 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -26759,7 +27458,7 @@
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -26767,7 +27466,7 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -26775,7 +27474,7 @@
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -26783,7 +27482,7 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -26791,7 +27490,7 @@
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -26799,7 +27498,7 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -26807,7 +27506,7 @@
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -26815,7 +27514,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -26823,7 +27522,7 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -26831,7 +27530,7 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -26839,7 +27538,7 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -26847,7 +27546,7 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="54">
@@ -26855,7 +27554,7 @@
         <v>2</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -26863,7 +27562,7 @@
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -26871,7 +27570,7 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -26879,7 +27578,7 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="36">
@@ -26887,7 +27586,7 @@
         <v>2</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -26905,7 +27604,7 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -26913,7 +27612,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -26921,7 +27620,7 @@
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -26929,7 +27628,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -26937,7 +27636,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -26945,7 +27644,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -26958,7 +27657,7 @@
         <v>2</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -26966,7 +27665,7 @@
         <v>4</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -26974,7 +27673,7 @@
         <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -26982,7 +27681,7 @@
         <v>4</v>
       </c>
       <c r="B100" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="36">
@@ -26990,7 +27689,7 @@
         <v>2</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -26998,7 +27697,7 @@
         <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -27011,7 +27710,7 @@
         <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -27019,7 +27718,7 @@
         <v>2</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -27027,7 +27726,7 @@
         <v>4</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -27035,7 +27734,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -27043,7 +27742,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -27051,7 +27750,7 @@
         <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -27059,7 +27758,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -27067,7 +27766,7 @@
         <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="54">
@@ -27075,7 +27774,7 @@
         <v>2</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -27083,7 +27782,7 @@
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -27091,7 +27790,7 @@
         <v>2</v>
       </c>
       <c r="B114" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -27099,7 +27798,7 @@
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="36">
@@ -27107,7 +27806,7 @@
         <v>2</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -27125,7 +27824,7 @@
         <v>4</v>
       </c>
       <c r="B119" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -27133,7 +27832,7 @@
         <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -27141,7 +27840,7 @@
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -27149,7 +27848,7 @@
         <v>2</v>
       </c>
       <c r="B122" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -27157,7 +27856,7 @@
         <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -27165,7 +27864,7 @@
         <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -27173,7 +27872,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -27181,7 +27880,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -27189,7 +27888,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -27197,7 +27896,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -27270,7 +27969,7 @@
         <v>2</v>
       </c>
       <c r="B142" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -27278,7 +27977,7 @@
         <v>2</v>
       </c>
       <c r="B143" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -27286,7 +27985,7 @@
         <v>2</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -27294,7 +27993,7 @@
         <v>13</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -27302,7 +28001,7 @@
         <v>4</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -27310,7 +28009,7 @@
         <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -27318,7 +28017,7 @@
         <v>2</v>
       </c>
       <c r="B148" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -27326,7 +28025,7 @@
         <v>2</v>
       </c>
       <c r="B149" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -27334,7 +28033,7 @@
         <v>4</v>
       </c>
       <c r="B150" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -27342,7 +28041,7 @@
         <v>2</v>
       </c>
       <c r="B151" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -27350,7 +28049,7 @@
         <v>2</v>
       </c>
       <c r="B152" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -27358,7 +28057,7 @@
         <v>2</v>
       </c>
       <c r="B153" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -27366,7 +28065,7 @@
         <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -27374,7 +28073,7 @@
         <v>2</v>
       </c>
       <c r="B155" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -27382,7 +28081,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -27390,7 +28089,7 @@
         <v>13</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -27398,7 +28097,7 @@
         <v>4</v>
       </c>
       <c r="B158" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -27406,7 +28105,7 @@
         <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -27414,7 +28113,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -27422,7 +28121,7 @@
         <v>13</v>
       </c>
       <c r="B161" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -27430,7 +28129,7 @@
         <v>4</v>
       </c>
       <c r="B162" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -27438,7 +28137,7 @@
         <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -27446,7 +28145,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -27454,7 +28153,7 @@
         <v>13</v>
       </c>
       <c r="B165" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -27477,4 +28176,2545 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA9DF8-3632-FD47-938F-DB511D31DF3F}">
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="288">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="144">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B62" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="54">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="36">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="54">
+      <c r="A84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="36">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="54">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="36">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="54">
+      <c r="A113" t="s">
+        <v>2</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="36">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>2</v>
+      </c>
+      <c r="B121" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>2</v>
+      </c>
+      <c r="B125" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="54">
+      <c r="A130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>4</v>
+      </c>
+      <c r="B131" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+      <c r="B132" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+      <c r="B133" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="36">
+      <c r="A134" t="s">
+        <v>2</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>4</v>
+      </c>
+      <c r="B137" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>2</v>
+      </c>
+      <c r="B138" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>4</v>
+      </c>
+      <c r="B139" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+      <c r="B140" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+      <c r="B141" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+      <c r="B142" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="B166" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{2D56B466-BB7B-9C4C-934D-1A768E45A12D}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{A7039F34-FABB-A149-A02B-C176F2E2A508}"/>
+    <hyperlink ref="B19" r:id="rId3" xr:uid="{3A7CBAA9-52E2-384A-93F2-5AF945CC38B3}"/>
+    <hyperlink ref="B22" r:id="rId4" xr:uid="{9E588BE6-EB74-D14E-AC9C-8061899B8B06}"/>
+    <hyperlink ref="B34" r:id="rId5" xr:uid="{E949288D-0580-3043-9B75-C420B3701347}"/>
+    <hyperlink ref="B40" r:id="rId6" xr:uid="{35D37EBD-3605-0643-B7D3-641007E9E3B9}"/>
+    <hyperlink ref="B52" r:id="rId7" xr:uid="{03E5A7F4-6371-6242-A27F-7E8FD8E0312F}"/>
+    <hyperlink ref="B55" r:id="rId8" xr:uid="{28C41CB2-E2E6-FC4F-A33F-8F87DAE4E1EE}"/>
+    <hyperlink ref="B69" r:id="rId9" xr:uid="{90076E61-2908-E64D-BA1C-255159F05506}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74CCB46-BC16-E14C-8293-BB36D1DBA3CF}">
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="54">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="36">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B84" s="2"/>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="54">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="36">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="54">
+      <c r="A113" t="s">
+        <v>2</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="36">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+      <c r="B118" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>2</v>
+      </c>
+      <c r="B121" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>2</v>
+      </c>
+      <c r="B125" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B130" s="2"/>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>2</v>
+      </c>
+      <c r="B145" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="B166" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{D2183ABA-1511-A14E-8F30-56E886D4BB66}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{8A5578CB-CCEB-054B-9742-751B29C8D0CD}"/>
+    <hyperlink ref="B19" r:id="rId3" xr:uid="{A2412F38-E188-1044-B28E-D3D48DBBF94E}"/>
+    <hyperlink ref="B22" r:id="rId4" xr:uid="{6C776942-F9EA-C542-B8B9-0B7FF5F19A7E}"/>
+    <hyperlink ref="B31" r:id="rId5" xr:uid="{0ADB1F35-EA3B-374A-AE68-F09A786A977A}"/>
+    <hyperlink ref="B34" r:id="rId6" xr:uid="{EF6D1136-D9BE-9B4C-9B7A-D188346F35A5}"/>
+    <hyperlink ref="B37" r:id="rId7" xr:uid="{4EC701F7-E119-F249-861A-610173F9E65C}"/>
+    <hyperlink ref="B40" r:id="rId8" xr:uid="{766E99F5-7572-024F-8899-3A45117DBF66}"/>
+    <hyperlink ref="B49" r:id="rId9" xr:uid="{477D08B9-F00E-3E4D-A455-644A1608E318}"/>
+    <hyperlink ref="B52" r:id="rId10" xr:uid="{C9C9B79B-4D53-8043-8BE3-BD7A93674F5E}"/>
+    <hyperlink ref="B55" r:id="rId11" xr:uid="{7861500E-49AB-E246-98F5-9E4B6431CBC2}"/>
+    <hyperlink ref="B69" r:id="rId12" xr:uid="{19E23D58-A01D-144F-B4C4-106B7B8CE1A8}"/>
+    <hyperlink ref="B104" r:id="rId13" xr:uid="{A0C9FC09-AFBB-5B49-A901-B658DC8598A3}"/>
+    <hyperlink ref="B119" r:id="rId14" xr:uid="{104356C4-1C2A-2C47-A1C9-33D2A07F8972}"/>
+    <hyperlink ref="B146" r:id="rId15" xr:uid="{FA2B346B-942D-B74A-AC08-28C4D24AA309}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>
--- a/ai-gate/copy.xlsx
+++ b/ai-gate/copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C772067C-99E9-484A-8429-ABC552EEC542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC172FE6-AE50-E24D-AC0A-BDF6AD20994E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="AFRICA_FR" sheetId="4" r:id="rId3"/>
     <sheet name="BE_FR" sheetId="5" r:id="rId4"/>
     <sheet name="TN_FR" sheetId="6" r:id="rId5"/>
+    <sheet name="SK" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="575">
   <si>
     <t>Type</t>
   </si>
@@ -23987,12 +23988,3626 @@
                       Powers everything you do</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>Ke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sa automaticky rozsvieti svetlo, okolo prechádza žena. Na obrazovke sa objaví veta „Múdro vníma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“.
+Muž a žena sa objímajú, ke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sa aktivuje reproduktor XBOOM, sprevádzaný frázou „“Hlboké porozumenie".
+Muž sedí smutne na sedadle vodi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a. Zobrazí sa logo umelej inteligencie LG s frázou „Starostlivo a srde</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ne“ LG AI reaguje hlasovou interakciou. Nižšie sa zobrazí fráza „Pre váš úžasný život“.
+XBOOM, televízor a rodina sediaca na pohovke so psom sa zobrazia v jednom zábere.
+Matka a syn spolo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ne používajú prá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ku. Zobrazí sa fráza „Pre váš život bez námahy“.
+Scény matky a syna, detailný záber na voli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI Wash a muža používajúceho notebook LG gram sú prekryté do jedného záberu s frázou ,,Pre váš život bez námahy".
+Muž a žena sedia na predných sedadlách auta. Medzi nimi sa zobrazuje logo LG AI spolu s frázou „Pre váš dobrý život“.
+Osoba vchádza do kancelárie so svojím psom. V reakcii na to sa zapne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ka vzduchu.
+Závere</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ný záber: biele pozadie s logom LG AI a frázou „Láskavá inteligencia pre VÁS“.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;span class="gradient-text" data-tp="copy"&gt;Láskavá inteligencia&lt;/span&gt; pre VÁS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ikona posúvania nadol</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nádherný život</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bezstarostný život</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spokojný život</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Umelá inteligencia LG rozumie vášmu životu a vylepšuje zážitky, aby bol váš život plný nádherných okamihov.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Muž a žena sedia na pohovke a sledujú v obýva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ke futbalový prenos na televízore LG . Scéna sa zmení a muž a žena sa objímajú.
+Kamera sa zameria na LG XBOOM ved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a nich.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zistite viac</t>
+  </si>
+  <si>
+    <t>Pre váš nádherný život</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/televizory/lg-oled55c5elb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Predný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt LG OLED evo AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/oled-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Predný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt LG OLED AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/qned-televizie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Predný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt LG QNED AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/nanocell-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Predný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt LG NanoCell AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Umelá inteligencia LG rozpozná vaše potreby a predloží riešenia, aby váš život plynul bez námahy pod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a vášho rytmu.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Matka a syn spolo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ne používajú prá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ku LG s umelou inteligenciou a otá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aním ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a aktivujú funkciu AI Wash. V tej istej sekvencii sa objaví muž, ktorý používa prenosný po</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>íta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LG gram.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre váš bezstarostný život</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/chladnicky/lg-gmg960evee</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Predný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt LG InstaView AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG AI sa stará o vás, váš priestor a planétu, aby bol váš život spokojný, presne pod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a vašich predstáv.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Do kancelárie vojde muž so psím vodítkom. Muž na sedadle vodi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a vyzerá smutne, ke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mu LG AI ukazuje rodinnú fotografiu. Na displeji vozidla sa v detailnom zábere zobrazí, ako LG AI na</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>íta mapu a vráti sa k spomienke.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre váš spokojný život</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/cz/bytove-klimatizace/bytove-klimatizace</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Predný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt LG DUALCOOL AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Bo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ný poh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ad na produkt ADAS vision</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Výber ponuky kávy s výzvou asistenta AI, interakcia používate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a s dotykovým rozhraním pohá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aným multimodálnym riešením HMI s umelou inteligenciou</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Spotrebi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Klimatizácie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" alt="LG AI TV" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Dokáže uspokoji</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> všetky vaše potreby v oblasti zábavy</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG AI TV sa u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>í vaše divácke preferencie a chápe váš životný štýl, aby optimalizovala každý aspekt vášho televízneho zážitku a vytvorila ideálnu personalizovanú zábavu presne pre vás.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Nad ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>om LG Magic Remote sa zobrazujú funkcie ako AI Voice ID, AI Search, AI Chatbot, AI Concierge, AI Picture Wizard a AI Sound Wizard.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/cz/tv-a-soundbars/ai-tv/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Na obrazovke televízora LG OLED je domovská stránka systému webOS 25 plná aplikácií a zábavného obsahu. Pri televízore sa nachádza dia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kový ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LG AI Magic Remote, ktorého tla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>idlo AI je zvýraznené, akoby ho používate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aktivoval hlasom. Ved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a neho je re</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ová bublina „“navrhni film, ktorý sa mi bude pá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>„“.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Vyh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adávanie pomocou AI</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Obrazovka televízora LG OLED, ktorá ukazuje, ako funguje vyh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adávanie s umelou inteligenciou. Otvorí sa malé okno chatu, ktoré ukazuje, ako sa používate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pýtal na dostupné športové hry. Vyh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adávanie AI odpovedalo prostredníctvom chatu a zobrazením miniatúr rôzneho dostupného obsahu. K dispozícii je aj ponuka na položenie otázky Microsoft Copilot.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Používanie dia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kového ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a LG AI Magic Remote. Krátkym stla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ením tla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>idla AI sa na obrazovke televízora OLED aktivuje asistent AI, ktorý potom navrhuje k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ú</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ové slová.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Na </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>avej strane obrazovky sa nachádza rozhranie Chatbot AI. Používate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oznámi chatbotovi, že obrazovka je príliš tmavá, a chatbot ponúkne riešenie požiadavky.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Žena spievajúca do mikrofónu so slúchadlami, zvýraznená vylepšením zvuku procesorom LG α11 AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Dia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kový ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI Magic</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Dve prepojené scény s ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>om LG AI Magic Remote pred televízorom - prvá zobrazuje sci-fi scénu, druhá zobrazuje domovskú obrazovku s personalizovaným obsahom</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*Funkcie umelej inteligencie LG využívajú vyškolené algoritmy založené na hlbokom u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ení na zvýšenie rozlíšenia obrazu a zmiešavanie zvuku v reálnom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ase.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**Všetky televízory LG so systémom webOS 24 sú vybavené funkciou AI Customization, okrem televízorov bez svetelných senzorov.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" alt="LG AI Audio" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Znie to jedine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ne</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG xboom AI analyzuje a upravuje zvuk tak, aby vyhovoval žánru a priestoru. V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aka osvetleniu AI, ktoré zlepšuje atmosféru a harmonizuje s hudbou, si môžete vychutna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> zvuk a atmosféru unikátne a správne.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Užite si nový zvukový zážitok s technológiou &lt;br&gt;
+                          LG xboom AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/audio-systemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Žena a muž sa objímajú v obýva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ke a ved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a nich je zapnutý reproduktor XBOOM.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reproduktor LG XBOOM s režimami zvuku AI vrátane Bass Boost, Voice Enhance a Standard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI zvuk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI osvetlenie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reproduktor LG XBOOM s osvetlením AI, ktoré sa prispôsobuje hlasovým, ambientným a párty režimom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reproduktor LG XBOOM umiestnený na stole v </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ervenej miestnosti so stenami s mriežkovým vzorom a moderným nábytkom</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI kalibrácia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Technológia LG WashTower AI rozpoznáva, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o periete, a poskytuje optimalizované pranie pre citlivú starostlivos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o tkaniny, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ím zakaždým zaistí dokonalé vypranie každej náplne.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" alt="Spotrebi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ite si každú zá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>až</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/pracky/lg-wt1210wwf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Vstavaná prá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ka a suši</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ka LG v modernej prá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ovni s drevenými skri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ami a lavicami na sedenie</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Ru</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>né nastavenie cyklu AI Wash na prá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ke LG pomocou inteligentného voli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Výber cyklu AI Dry na suši</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ke LG pomocou digitálneho ovládacieho voli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI pranie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI sušenie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*Tento produkt sa bude vo vybraných krajinách uvo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> postupne.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>**Snímanie pomocou systému AI sa aktivuje, ke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> je hmotnos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nákplne nižšia ako 6 kg.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>***AI Wash by sa malo používa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> len s podobnými typmi tkanín [nie všetky tkaniny sú rozpoznané] a vhodným pracím prostriedkom.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-mobile.svg" alt="Klimatizácie" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Pohodlie s dokonale vyladeným chladením</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG DUALCOOL AI sa stará o optimálnu klímu, udržiava pohodlie a zárove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> optimalizuje energetickú ú</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>innos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ím pomáha šetri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> náklady. S LG AI Air zažijete dokonale prispôsobené chladenie pre vaše pohodlie.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pomocou technológie ThinQ AI, klimatizácia LG DUAL Inverter chladí modernú obývaciu izbu, v ktorej na pohovke sedí žena.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zažite optimalizovaný dizajn s technológiou &lt;br&gt;
+                          LG AI Air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Žena relaxuje v inteligentnej obýva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ke, zatia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o klimatizácia LG AI automaticky upravuje teplotu, prúdenie vzduchu a vlhkos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rozhranie smartfónu zobrazujúce graf spotreby energie pred klimatizáciou LG, zvýraznenie AI kW Manager na efektívne monitorovanie energie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manažér AI kW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*Air AI sa dá ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pomocou dia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kového ovládania a ThinQ.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**AI Air je k dispozícii v režime chladenia aj vykurovania.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>***Po</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as používania AI Air sa objem vzduchu a smer prúdenia vzduchu automaticky upravujú pod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a situácie a AI Air sa vypne, ke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sa zmení smer prúdenia vzduchu.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>****Pri aktivácii funkcie AI Air radarový sníma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> zistí polohu používate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a a automaticky aktivuje priamy/nepriamy smer  prúdenia vzduchu.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*****Vzdialenos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> snímania radarového sníma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a je do 5 m, pri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>om v závislosti od prostredia inštalácie a používania výrobku môžu by</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> rozdiely vo vzdialenosti snímania.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>******Táto funkcia funguje len s modelmi, ktoré majú radarové sníma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ThinQ® pomáha prinies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> život do reality</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Platforma pre inteligentné spotrebi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e a zariadenia LG ThinQ vám umožní ovláda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a využíva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pohodlie na dosah ruky, aby vám pomohla zjednoduši</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> život a užíva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> si pohodlie domova.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/sk/domace-spotrebice/thinq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>Č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lovek drží smartfón s otvorenou aplikáciou LG ThinQ a po</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as pitia kávy spravuje inteligentné domáce zariadenia.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>V modernej inteligentnej kuchyni žena pomocou hlasového príkazu spúš</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a prá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ku s umelou inteligenciou LG ThinQ, zatia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ľ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">o muž v úzadí na pohovke </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>íta.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jednoduché ovládanie s hlasovým asistentom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Povedzte zariadeniu LG, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o presne potrebujete, a reproduktor s umelou inteligenciou si vás vypo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uje a skontroluje priebeh cyklu a dá vám to na vedomie.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>a displeji smartfónu sa zobrazuje aplikácia LG ThinQ, ktorá ovláda vstavanú rúru LG InstaView Slide-In Range a umož</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uje efektívnu údržbu výrobku v kuchyni.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Efektívna údržba produktov</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prostredníctvom aplikácie LG ThinQ môžete kontrolova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> svoj spotrebi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LG, s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ahova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nové cykly, sledova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> priebeh cyklu a mnoho </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alšieho.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Viac o LG Láskavá inteligencia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Spolo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LG posil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uje vedúce postavenie v oblasti kybernetickej bezpe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nosti v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aka akreditácii KOLAS na testovanie kybernetickej bezpe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nosti IoT</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Riadiaci pracovník spolo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nosti LG Electronics s certifikátom o akreditácii pre kybernetickú bezpe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, v pozadí grafika digitálnej bezpe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nosti</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Návštevníci si na výstave technológií obzerajú zakrivený LED displej LG so sloganom "Life's Good 24/7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>V spolo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nosti LG sme si kládli otázku: Pre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o by mala umelá inteligencia existova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>? &lt;br&gt;
+              Po dlhom uvažovaní sme našli odpove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. &lt;br&gt;&lt;br&gt;
+              Pre nás AI presahuje rámec umelej inteligencie - je to láskavá inteligencia. &lt;br&gt;&lt;br&gt;
+              As AI becomes a part of our daily lives, &lt;br&gt;
+              by mala pomôc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vytvori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lepší život, ktorý si všetci zaslúžime. &lt;br&gt;&lt;br&gt;
+              Preto LG AI za</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ína s Vami láskyplne prostredníctvom &lt;br&gt;
+              vnímania a porozumenia, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alej sa stará o Váš život.
+              &lt;strong&gt;Zistite, ako je Life's Good s umelou inteligenciou LG&lt;/strong&gt;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zoznámte sa s novou generáciou &lt;br&gt;
+                          LG AI TV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Objavte nový spôsob života s technológiou &lt;br&gt;
+                           LG AI Core Tech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>****AI Dry je k dispozícii len pre nápl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> s hmotnos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ť</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ou pod 5 kg a s tkaninami s rovnakou úrov</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ň</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ou nasiakavosti.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -24037,6 +27652,21 @@
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -24064,7 +27694,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -24076,6 +27706,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -30717,4 +34348,1276 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB88BCCA-2AF6-E44E-B910-B08F30094E46}">
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="198">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="144">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="36">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="162">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="36">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="162">
+      <c r="A84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="36">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="162">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="36">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="162">
+      <c r="A113" t="s">
+        <v>2</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="36">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+      <c r="B118" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>2</v>
+      </c>
+      <c r="B121" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>2</v>
+      </c>
+      <c r="B125" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="180">
+      <c r="A130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>2</v>
+      </c>
+      <c r="B145" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="B166" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{D9095DA6-4FB3-3E4D-BA09-A1CE936EDE60}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{B2C1A08E-7E9F-3347-BE49-1EBFEC8203D6}"/>
+    <hyperlink ref="B19" r:id="rId3" xr:uid="{7B7094D5-904B-6243-AE18-639FCAF73573}"/>
+    <hyperlink ref="B22" r:id="rId4" xr:uid="{DC2F17C5-C168-7D4E-B3A3-D3184EE355A4}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{0DBD1E02-D501-6F47-8235-B1EF430E6425}"/>
+    <hyperlink ref="B49" r:id="rId6" xr:uid="{65D86518-B361-C046-AA07-A7B023153E57}"/>
+    <hyperlink ref="B52" r:id="rId7" xr:uid="{C5836BD4-5EF4-F74A-8A97-5B8177650909}"/>
+    <hyperlink ref="B55" r:id="rId8" xr:uid="{83C99206-622F-3B48-89FA-CFD98D67A3D7}"/>
+    <hyperlink ref="B69" r:id="rId9" xr:uid="{D3DED111-D9FB-BB45-920B-0F4E6EB248F3}"/>
+    <hyperlink ref="B90" r:id="rId10" xr:uid="{239878BF-DFA5-DE4C-B568-A96D2227C65B}"/>
+    <hyperlink ref="B104" r:id="rId11" xr:uid="{9E2A6E74-DD39-4549-BDA8-74C7392F213C}"/>
+    <hyperlink ref="B119" r:id="rId12" xr:uid="{7858FB2A-1866-344E-8FCF-B7D4EC6E02B7}"/>
+    <hyperlink ref="B146" r:id="rId13" xr:uid="{47C04396-0651-ED4F-BB37-6687D5607853}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>
--- a/ai-gate/copy.xlsx
+++ b/ai-gate/copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC172FE6-AE50-E24D-AC0A-BDF6AD20994E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDA9A7C-59AD-454A-A2EA-25E8E93E9E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
@@ -14,13 +14,14 @@
     <sheet name="BE_FR" sheetId="5" r:id="rId4"/>
     <sheet name="TN_FR" sheetId="6" r:id="rId5"/>
     <sheet name="SK" sheetId="8" r:id="rId6"/>
+    <sheet name="BG" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="675">
   <si>
     <t>Type</t>
   </si>
@@ -27600,6 +27601,447 @@
       </rPr>
       <t>ou nasiakavosti.</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Една жена преминава, когато светлината се включва автоматично. На екрана се появява надпис „Сензитивност“.
+Мъж и жена се прегръщат, когато се активира високоговорителят на XBOOM, придружен от думата  „Разбиране“.
+Мъж седи тъжно на шофьорската седалка. Появява се логото на LG AI с надпис "Грижа".
+По телевизията се излъчва футболен мач. LG AI реагира с гласово взаимодействие. Отдолу се показва фразата „За вашия възхитителен живот“.
+XBOOM, телевизорът и семейство, седнало на дивана с кучето си, се появяват в един кадър.
+Майка и син използват заедно пералната машина. Появява се фразата „За вашия безпроблемен живот“.
+Сцените на майката и сина, близък план на AI Wash и мъж, който използва лаптопа LG gram, се наслагват в един кадър, като се появява фразата „За безпроблемен живот“.
+Мъж и жена седят на предните седалки на автомобил. Логото на LG AI се появява между тях, заедно с фразата „За вашия живот с грижа“.
+Човек влиза в офис с кучето си. Пречиствателят на въздуха се включва.
+Финален кадър: бял фон с логото на LG AI и фразата „Интелегентност с грижа за ВАС“.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;span class="gradient-text" data-tp="copy"&gt;Affectionate Intelligence&lt;/span&gt; за ВАС</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>В LG си задаваме въпроса: за какво трябва да съществува AI? &lt;br&gt;
+              След дълъг размисъл намерихме своя отговор. &lt;br&gt;&lt;br&gt;
+              За нас AI е нещо повече от изкуствен интелект - това е интелигентност с обич и грижа. &lt;br&gt;&lt;br&gt;
+              Тъй като AI става част от нашето ежедневие, &lt;br&gt;
+              той трябва да помогне за създаването на по-добър живот, който всички заслужаваме. &lt;br&gt;&lt;br&gt;
+              Ето защо AI на LG започва с обич към ВАС чрез &lt;br&gt;
+              сензитивност и разбиране, както и грижа за живота ви.
+              &lt;strong&gt;Открий как животът е хубав с  LG AI&lt;/strong&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Превъртете надолу иконата</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Прекрасен живот</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Безпроблемен живот</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Живот с грижа</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI разбира вашия живот и надгражда преживяванията, за да създаде  живот, изпълнен с прекрасни моменти.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мъж и жена седят на дивана и гледат футболно предаване на телевизор LG в хола. 
+Сцената се премества и мъжът и жената се прегръщат.
+Камерата се фокусира върху LG XBOOM до тях.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>За вашия прекрасен живот</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/oled-evo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG OLED evo AI продукти- фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Научете повече</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/oled-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG OLED AI продукти -фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/qned-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG QNED AI продукти- фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/nanocell-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG NanoCell AI продукти- фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI усеща вашите нужди и представя решения, чрез които да направи живота ви безгрижен и според избрания ритъм.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Майка и син използват заедно пералнята с LG AI, като завъртат копчето, за да активират функцията AI Wash. В същата сцена се появява мъж, който използва лаптоп LG gram.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>За вашия  безпроблемен живот</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/lg-washtower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG WashTower AI продукт- фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/peralni-mashini/lg-f4wr513sbw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG Washing Machine AI продукт- фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/hladilnitzi/lg-gsgv81pyll</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG InstaView AI продукт- фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG AI се грижи за вас, вашето пространство и за планетата, за да направи живота ви безгрижен.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>В офиса влиза мъж с каишка за куче. Мъжът на шофьорската седалка изглежда тъжен, когато LG AI му показва семейна снимка. Дисплеят на автомобила е показан в близък план, докато LG AI изважда карта и се връща към спомен.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>За вашия живот с грижа</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/klimatichna-tehnika/lg-p12snd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG DUALCOOL AI продукт с фронтален изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADAS vision система със страничен изглед</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Взаимодействие на потребителя със сензорен интерфейс, задвижван от мултимодално HMI решение с изкуствен интелект, избор на меню за кафе с подкана от асистент с изкуствен интелект.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ТВ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Аудио</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Бяла техника</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Климатична техника</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" alt="ТВ" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Evolves to satisfy your every entertainment need</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Телевизорът с изкуствен интелект на LG научава предпочитанията ви за гледане и разбира начина ви на живот, за да оптимизира всеки аспект на телевизионното ви изживяване, създавайки идеално персонализирано забавление точно за вас.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Над LG Magic Remote се показват функции като AI Chatbot, AI Picture Wizard и AI Sound Wizard.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Запознайте се със следващо поколение &lt;br&gt;
+                          LG AI TV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/televizori/ai-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Научно-фантастично съдържание се възпроизвежда на екрана на OLED телевизор LG. В лявата част на екрана е разположен интерфейсът на AI Chatbot. Потребителят съобщава на чатбота, че екранът е твърде тъмен, и чатботът предлага решения на искането.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Жена пее с микрофон със слушалки, с LG α11 AI Processor за подобряване на звука</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Две свързани сцени с LG AI Magic Remote пред телевизор - първата показва научнофантастична сцена, а втората - начален екран с персонализирано съдържание</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Функциите с изкуствен интелект на LG използват обучени алгоритми, базирани на дълбоко обучение, за увеличаване на мащаба на изображенията и смесване на звука в реално време.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**Всички телевизори LG webOS 24 разполагат с функция AI Customization, с изключение на тези без сензори за светлина.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" alt="Аудио" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Звук, който звучи по най-правилния начин</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG xboom AI анализира и настройва звука, за да отговаря на жанра и пространството. Чрез AI осветлението, което подобрява обстановката и хармонизира с музиката, можете да се насладите на звук и атмосфера по уникален начин.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Жена и мъж се прегръщат в хола, а до тях е включен високоговорителят на XBOOM.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Наслаждавайте се на ново звуково преживяване с &lt;br&gt;
+                          LG xboom AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG XBOOM говорител с AI звукови режими включва Bass Boost, Voice Enhance и Standard.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Звук</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LG XBOOM говорител с AI осветелние, което се адаптира към глас, околна среда и парти режим. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Осветление</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Калибриране</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Високоговорител LG XBOOM, поставен на маса в стая в червени тонове, със стени с решетъчни шарки и модерни мебели.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Този продукт все още не е наличен</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" alt="Бяла техника" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Освобождаване от обемите пране</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG WashTower AI разпознава какво перете, за да осигури оптимизирано изпиране за чувствителни тъкани, като ви гарантира, че без усилие ще усъвършенствате всяко зареждане, всеки път.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вградени пералня и сушилня LG в модерно перално помещение с дървени шкафове и пейки за сядане.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Открийте нов начин на живот с &lt;br&gt;
+                          LG AI Core Tech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/peralni-mashini/lg-aidd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ръчно регулиране на цикъла на пране AI на пералната машина LG с помощта на интелигентен контролен диск</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Пране</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Потребител, който избира AI Dry цикъл на сушилнята LG с помощта на цифровия контролен диск.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Сушене</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Този продукт ще бъде пуснат поетапно в избрани страни.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**Активира се сензорът за AI, когато товарът е под 6 kg.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***Измиването с AI трябва да се използва само с подобни видове тъкани [не всички тъкани се разпознават] и подходящ перилен препарат.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****AI Dry се предлага само за зареждания под 5 кг с тъкани със същите нива на абсорбция на влага.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-air-conditioning-eyebrow-logo-mobile.svg" alt="Климатична техника" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Комфорт с перфектно охлаждане</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG DUALCOOL AI се грижи за оптимален въздух, като ви осигурява комфорт и същевременно оптимизира енергийната ефективност, за да спести разходи. С LG AI Air се наслаждавайте на перфектно охлаждане за вашия комфорт.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Инверторният климатик LG DUAL охлажда модерна всекидневна, в която жена е седнала на дивана, благодарение на технологията ThinQ AI.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Оптимизиран комфорт с &lt;br&gt;
+                          LG AI Air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Жена релаксира в смарт всекидневна, докато климатикът LG AI автоматично регулира температурата, въздушния поток и влажността.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Въздух</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Интерфейс на смартфон, показващ графика на потреблението на енергия пред климатик LG, с подчертан AI kW Manager за ефективен мониторинг на енергията.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*AI Air може да се управлява с дистанционно управление и ThinQ.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>**AI Air се предлага в режими на охлаждане и отопление.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>***По време на използване на AI Air обемът на въздуха и посоката на вятъра се регулират автоматично в зависимост от ситуацията, а AI Air се изключва при промяна на посоката на вятъра.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>****Когато AI Air е активиран, радарният сензор открива местоположението на обекта и автоматично активира директния/непосредствения вятър.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*****Разстоянието на засичане на радарния сензор е до 5 м, като е възможно да има разлики в разстоянието на засичане в зависимост от средата на инсталиране и използване на продукта.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>******Тази функция работи само с модели, които имат радарни сензори.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThinQ® прави управлението да се случва лесно</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Приложение а за вашите интелигентни уреди и устройства, LG ThinQ предоставя контрол и удобство на ръка разстояние, за да ви помогне да опростите живота си и да се наслаждавате на домашния уют.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/bg/elektrodomakinski-uredi/thinq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Човек държи смартфон, в който е отворено приложението LG ThinQ, и управлява  домашни устройства, докато пие кафе.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Смартфонът показва приложението LG ThinQ за управление на фурната LG InstaView Slide-In Range, което позволява ефективна поддръжка на продукта в кухнята.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ефективна продуктова поддръжка</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Чрез приложението LG ThinQ проверявайте своя уред от LG, изтегляйте нови цикли, наблюдавайте използването  и много други.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Повече за LG Affectionate Intelligence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LG Electronics поддържа акредитация за киберсигурност с графика за цифрова сигурност. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG укрепва лидерството си в областта на киберсигурността с акредитацията на KOLAS за тестване на киберсигурността на IoT.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Посетители разглеждат извития LED дисплей на LG, представящ слогана „Life's Good 24/7“ на технологично изложение.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG представя на CES 2025 най-новите си иновации, задвижвани от „Аffectionate Intelligence“</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Говорител, който представя B2B решения с изкуствен интелект на сцената на събитие на LG.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG представя един ден от живота с „Аffectionate Intelligence“ на световната премиера на LG</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -35620,4 +36062,1256 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A991E548-02F4-F043-A91A-3C844B35EB11}">
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="234">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="144">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="54">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="162">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="36">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="162">
+      <c r="A84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="36">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="162">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="36">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="162">
+      <c r="A113" t="s">
+        <v>2</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="36">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>2</v>
+      </c>
+      <c r="B121" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>2</v>
+      </c>
+      <c r="B125" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B130" s="2"/>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>2</v>
+      </c>
+      <c r="B145" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="B166" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{5B01F28E-0A55-594E-94C5-5C81AD1C43E6}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{90B219FD-0D2E-2842-968D-050A0B1ADBF7}"/>
+    <hyperlink ref="B19" r:id="rId3" xr:uid="{BF54A870-5159-E24D-B344-D68CA27194B8}"/>
+    <hyperlink ref="B22" r:id="rId4" xr:uid="{564D10A8-DC3F-864E-A663-D03439698A51}"/>
+    <hyperlink ref="B31" r:id="rId5" xr:uid="{223BE860-1155-E84A-891B-13209FBD68C1}"/>
+    <hyperlink ref="B34" r:id="rId6" xr:uid="{3834B966-88C5-9745-A351-A06179BF7FE8}"/>
+    <hyperlink ref="B40" r:id="rId7" xr:uid="{F7ED3F57-484D-F84B-8703-1361220D4B64}"/>
+    <hyperlink ref="B49" r:id="rId8" xr:uid="{15330C5B-D989-F644-8B84-17C618A55C7B}"/>
+    <hyperlink ref="B52" r:id="rId9" xr:uid="{816926B0-D7D3-D74C-9E67-9C54B16996B4}"/>
+    <hyperlink ref="B55" r:id="rId10" xr:uid="{0F8E9FD9-FB4D-9C4C-8299-391F5D7AFC1B}"/>
+    <hyperlink ref="B69" r:id="rId11" xr:uid="{E11A81D7-8798-7047-88B8-445D374A06D3}"/>
+    <hyperlink ref="B104" r:id="rId12" xr:uid="{04E234A5-B841-1F4E-93C7-4353D245DCDE}"/>
+    <hyperlink ref="B146" r:id="rId13" xr:uid="{D24EA7E2-E0A9-0341-AE3E-E3CBCD1FC65E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>
--- a/ai-gate/copy.xlsx
+++ b/ai-gate/copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDA9A7C-59AD-454A-A2EA-25E8E93E9E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AA6F53-A498-3141-B1C3-2E9FA7D5F1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,14 @@
     <sheet name="TN_FR" sheetId="6" r:id="rId5"/>
     <sheet name="SK" sheetId="8" r:id="rId6"/>
     <sheet name="BG" sheetId="9" r:id="rId7"/>
+    <sheet name="LT" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="755">
   <si>
     <t>Type</t>
   </si>
@@ -28042,6 +28043,6863 @@
   </si>
   <si>
     <t>LG представя един ден от живота с „Аffectionate Intelligence“ на световната премиера на LG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Moteris praeina pro šal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, kai automatiškai </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sijungia šviesa. Ekrane pasirodo užrašas „Išmintingai jau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">iame“.
+Vyras ir moteris apsikabina, kai </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sijungia „XBOOM“ garsiakalbis, kartu išgirstama fraz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> „Giliai suprantame“.
+Vyras li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dnai s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>di vairuotojo vietoje. Pasirodo „LG AI“ logotipas su užrašu „Šiltai r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pinuosi“.
+Per televizori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> rodomos futbolo rungtyn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s. „LG AI“ atsako balso s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>veika. Žemiau rodoma fraz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> „Už j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> malon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“.
+Viename kadre matomi „XBOOM“, televizorius ir šeima, s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dinti ant sofos su savo šunimi.
+Motina ir s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nus kartu naudojasi skalbimo mašina. Pasirodo fraz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> „Už j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lengv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“.
+Motinos ir s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>naus, AI skalbimo mašinos ratuko stambus planas ir vyro, naudojan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>io „LG gram“ nešiojam</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kompiuter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, scenos sud</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">liotos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vien</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kadr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su užrašu „Už j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lengv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“.
+Vyras ir moteris s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>di automobilio priekin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>se s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dyn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>se. Tarp j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> rodomas „LG AI“ logotipas ir užrašas „Už j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gerai priži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">“.
+Žmogus </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">eina </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> biur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su savo šunimi. Oro valytuvas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sijungia reaguodamas.
+Paskutinis kadras: baltas fonas su LG dirbtinio intelekto logotipu ir užrašu „Meilus intelektas JUMS“.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;span class="gradient-text" data-tp="copy"&gt;Jautrus intelektas&lt;/span&gt; JUMS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG“ kompanijoje mes sav</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ę</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s klaus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>me: kam tur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egzistuoti dirbtinis intelektas? &lt;br&gt;
+              Po ilg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> apm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stym</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> radome atsakym</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. &lt;br&gt;&lt;br&gt;
+              Mums dirbtinis intelektas yra daugiau nei dirbtinis intelektas – tai jautrus intelektas. &lt;br&gt;&lt;br&gt;
+              Dirbtiniui tapus m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kasdienio gyvenimo dalimi, &lt;br&gt;
+              jis tur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ti kurti geresn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kurio visi nusipeln</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>me. &lt;br&gt;&lt;br&gt;
+              Štai kod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>l „LG“ dirbtinis intelektas prasideda nuo J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>Ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>Ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – per meil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> poj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir supratim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, &lt;br&gt;
+              toliau r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pinantis j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenimu.
+              &lt;strong&gt;Atraskite, koks gyvenimas geras su LG dirbtiniu intelektu&lt;/strong&gt;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slinkimo žemyn piktograma</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuostabus gyvenimas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Gyvenimas be pastang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Gerai priži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rimas gyvenimas</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG AI“ supranta j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir patobulina patirt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kad j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenimas b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kupinas maloni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> akimirk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Vyras ir moteris s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>di ant sofos ir ži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ri futbolo transliacij</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> per LG televizori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> svetain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je. Vaizdas pasikei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ia, vyras ir moteris apsikabina.
+Kamera sufokusuoja šalia j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> esant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LG XBOOM.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Už j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> džiaugsming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/oled-evo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>„LG OLED evo AI“ gaminio priekinis vaizdas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sužinokite daugiau</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/oled-televizoriai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG OLED dirbtinio intelekto gaminio priekinis vaizdas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/qned-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG QNED dirbtinio intelekto gaminio priekinis vaizdas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/nanocell-televizoriai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>„LG NanoCell“ dirbtinio intelekto gaminio priekinis vaizdas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG dirbtinis intelektas jau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ia j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> poreikius ir si</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lo sprendimus, kad j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenimas sklandžiai tek</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pagal j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ritm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Motina ir s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nus kartu naudojasi LG dirbtiniu intelektu valdoma skalbimo mašina ir pasuka ratuk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, kad </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jungt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dirbtinio intelekto skalbim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Toje pa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ioje sekoje pasirodo vyras, naudojantis LG nešiojam</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kompiuter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lengvam gyvenimui</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/skalbimo-masinos/lg-wt1210bbf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>„LG WashTower“ dirbtinio intelekto gaminio priekinis vaizdas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/saldytuvai/lg-gmg960evee</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG InstaView dirbtinio intelekto gaminio priekinis vaizdas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG AI“ r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pinasi jumis, j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> erdve ir planeta, kad j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenimas b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gerai priži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rimas, b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tent toks, kokio trokštate.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vyras </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">eina </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> biur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> laikydamas šuns pavad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Vyras vairuotojo vietoje atrodo li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dnas, kai LG AI rodo jam šeimos nuotrauk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Automobilio ekranas rodomas stambaus plano režimu, kai LG AI atveria žem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir prisimena prisiminim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gerai priži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rimam gyvenimui</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADAS vaizdo sistemos gaminio vaizdas iš šono</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Vartotojas s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>veikauja su jutikliniu ekranu, kur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> palaiko multimodalinis dirbtinio intelekto HMI sprendimas, renkasi kavos meniu su dirbtinio intelekto asistento raginimu</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Buitin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> technika</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-tv-eyebrow-logo-mobile.svg" alt="LG AI TV" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Tobul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ja, kad patenkint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> visus j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pramog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> poreikius</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG AI TV“ išmoksta j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jimo pageidavimus ir supranta j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenimo b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kad optimizuot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kiekvien</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> televizijos ži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jimo patirties aspekt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, sukurdamas idealiai suasmenint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pramog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tik jums.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Susipažinkite su naujos kartos &lt;br&gt;
+                           LG dirbtinio intelekto televizoriumi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/televizoriai/ai-tv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG OLED televizoriaus ekrane rodomas „webOS 25“ pagrindinis puslapis, kuriame gausu program</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir pramoginio turinio. Šalia televizoriaus yra LG dirbtinio intelekto „Magic Remote“ nuotolinio valdymo pultas, kurio dirbtinio intelekto mygtukas paryškintas taip, tarsi b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aktyvuotas naudotojo balsu. Šalia jo yra kalbos burbulas su užrašu „pasi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lykite film</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kuris man patikt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG OLED televizoriaus ekrane rodoma, kaip veikia dirbtinio intelekto paieška. Atidarytas nedidelis pokalbi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> langas, kuriame rodoma, kaip vartotojas paklaus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kokie sporto žaidimai yra prieinami. Dirbtinio intelekto paieška atsak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> per pokalb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir rodydama skirtingo prieinamo turinio miniati</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ras. Taip pat rodomas raginimas užduoti klausim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> „Microsoft Copilot“.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Naudojamas LG dirbtinio intelekto „Magic Remote“ nuotolinio valdymo pultas. Trumpai paspaudus dirbtinio intelekto mygtuk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, OLED televizoriaus ekrane </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jungiamas dirbtinio intelekto asistentas, kuris pasi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lo raktinius žodžius.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mokslin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s fantastikos turinys rodomas LG OLED televizoriaus ekrane. Kair</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je ekrano pus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je yra dirbtinio intelekto pokalbi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> roboto s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>saja. Vartotojas praneša pokalbi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> robotui, kad ekranas per tamsus, o pokalbi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> robotas pasi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">lo atsakymus </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> užklaus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Moteris, dainuojanti </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mikrofon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su ausin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mis, paryškinta LG α11 dirbtinio intelekto procesoriaus garso stiprinimo funkcija</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Dvi sujungtos scenos su LG dirbtinio intelekto „Magic Remote“ nuotolinio valdymo pultu priešais televizori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – pirmoje rodoma mokslin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s fantastikos scena, antroje – pagrindinis ekranas su suasmenintu turiniu</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*„LG“ dirbtinio intelekto funkcijos naudoja giliojo mokymosi pagrindu parengtus algoritmus, skirtus vaizdo konvertavimui ir garso maišymui realiuoju laiku.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>**Visi „LG webOS 24“ televizoriai turi dirbtinio intelekto pritaikymo funkcij</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, išskyrus tuos, kurie neturi šviesos jutikli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-audio-eyebrow-logo-mobile.svg" alt="LG AI Audio" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Skamba išskirtinai teisingai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG xboom AI“ analizuoja ir pritaiko gars</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> prie žanro ir erdv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s. Dirbtinio apšvietimo d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ka, kuris pagerina atmosfer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir dera su j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muzika, galite m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gautis unikaliu garsu ir atmosfera.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Moteris ir vyras apsikabina svetain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je, šalia j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jungtas XBOOM garsiakalbis.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gaukit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s nauja garso patirtimi &lt;br&gt;
+                         su „LG xboom AI“</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LG XBOOM garsiakalbis su dirbtinio intelekto garso režimais, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skaitant žem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dažni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> stiprinim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, balso sustiprinim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir standartin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dirbtinio intelekto garsas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG XBOOM garsiakalbis su dirbtinio intelekto apšvietimu, kuris prisitaiko prie balso, aplinkos ir vakar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lio režim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dirbtinio intelekto apšvietimas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG XBOOM garsiakalbis pastatytas ant stalo raudoname kambaryje su tinklelio rašto sienomis ir moderniais baldais</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DI kalibravimas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*Šis produktas kol kas n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ra prieinamas.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;picture&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-desktop.svg" media="(min-width: 769px)"&gt;
+                        &lt;source srcset="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" media="(max-width: 768px)"&gt;
+                        &lt;img src="./assets/image/ai-gate-image-product-category-appliances-eyebrow-logo-mobile.svg" alt="Buitin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> technika" class="eyebrow-logo" loading="lazy"&gt;
+                      &lt;/picture&gt;
+                      Palengvinkite kiekvien</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> savo našt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG WashTower“ dirbtinis intelektas jau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ia, k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> skalbiate, kad optimizuot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> skalbim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jautri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> audini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> prieži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rai ir užtikrint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, jog kiekvienas skalbimas b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tobulas kiekvien</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>Į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>montuojama LG skalbimo mašina ir džiovykl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> modernioje skalbykloje su medin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mis spintel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mis ir suoliukais</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Atraskite nauj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyvenimo b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;br&gt;
+                           su „LG AI Core Tech“</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Rankinis dirbtinio intelekto skalbimo ciklo reguliavimas LG skalbimo mašinoje naudojant išman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> valdymo ratuk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Vartotojas pasirenka AI džiovinimo cikl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LG džiovykl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je naudodamas skaitmenin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> valdymo ratuk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Šis produktas bus palaipsniui pristatomas pasirinktose šalyse.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">**AI jutiklis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jungiamas, kai skalbini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> svoris yra mažesnis nei 6 kg.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>***AI skalbimas tur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ti naudojamas tik su panašiais audini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tipais [ne visi audiniai aptinkami] ir tinkamu skalbikliu.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>****AI džiovinimas galimas tik su skalbini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kiekiu iki 5 kg, kai audini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s sug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rimo lygis yra toks pat.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>„ThinQ®“ padeda gyventi sklandžiai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„ThinQ“ – tai platforma j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> išmaniesiems LG prietaisams ir </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renginiams, suteikianti valdym</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir patogum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vos už keli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> žingsni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kad pad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jums supaprastinti gyvenim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gautis nam</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jaukumu.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Asmuo laiko išman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> telefon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su atidaryta „LG ThinQ“ program</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>le, valdo išmaniuosius nam</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renginius ir geria kav</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Šiuolaikin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je išmaniojoje virtuv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">je moteris balso komanda </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jungia skalbimo mašin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su „LG ThinQ AI“, o vyras fone skaito ant sofos.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Paprastas valdymas naudojant balso asistent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Pasakykite savo LG prietaisui, ko jums tiksliai reikia, tiesiog ištardami tai, o dirbtinio intelekto garsiakalbis išklausys ir patikrins cikl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, kad jums pranešt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Išmaniajame telefone rodoma „LG ThinQ“ program</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, valdanti „LG InstaView Slide-In Range“ orkait</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ę</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, leidžian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>č</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> efektyviai priži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ti gaminius virtuv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Efektyvi gamini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> prieži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ra</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Naudodamiesi „LG ThinQ“ program</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>le, patikrinkite savo „LG“ prietais</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, atsisi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skite naujus ciklus, steb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kite cikl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> naudojim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ir dar daugiau.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Daugiau apie LG meil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intelekt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>„LG Electronics“ vadovas laiko kibernetinio saugumo akreditacijos sertifikat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, fone – skaitmeninio saugumo grafika</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG stiprina kibernetinio saugumo lyderyst</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ę</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gydama KOLAS daikt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> interneto kibernetinio saugumo testavimo akreditacij</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Praneš</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jas LG renginyje scenoje pristato dirbtiniu intelektu pagr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>į</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stus B2B sprendimus</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LG pasaulin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ė</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je premjeroje pristato dien</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su „meiliuoju intelektu“</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Technologij</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ų</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parodoje lankytojai apži</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ri LG lenkt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LED ekran</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> su š</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ū</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kiu „Gyvenimas geras vis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> par</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ą</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -37314,4 +44172,1202 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F68D2E8-3405-F648-94E4-AE9CECB48D2A}">
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="234">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="144">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="36">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="162">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="36">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="162">
+      <c r="A84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="36">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="162">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="36">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>2</v>
+      </c>
+      <c r="B113" s="2"/>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B130" s="2"/>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="B166" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{84B8A12D-E639-E743-9F54-5B8E0A50DFFB}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{C6AA4341-FF93-4546-BFDB-ACBF9874B543}"/>
+    <hyperlink ref="B19" r:id="rId3" xr:uid="{17299F4F-E584-4540-8D4E-4D62DCB0A0D8}"/>
+    <hyperlink ref="B22" r:id="rId4" xr:uid="{32B60D72-6871-3947-ADE1-C0C185DC9F06}"/>
+    <hyperlink ref="B31" r:id="rId5" xr:uid="{80FB957E-2C78-C748-8C7C-604471748F6F}"/>
+    <hyperlink ref="B40" r:id="rId6" xr:uid="{D28AEC01-C06D-F640-BFBD-52BF87C254D0}"/>
+    <hyperlink ref="B52" r:id="rId7" xr:uid="{F985EF13-08CE-2543-9925-CA924D12A96E}"/>
+    <hyperlink ref="B55" r:id="rId8" xr:uid="{991E449C-1E5D-2540-A81B-3820F800C12A}"/>
+    <hyperlink ref="B69" r:id="rId9" xr:uid="{68709F3E-77D9-D74C-94D4-3D7FC3C90839}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>